--- a/Deliverables/Phase2/Sprint1/asvs/v4-ASVS-checklist-en.xlsx
+++ b/Deliverables/Phase2/Sprint1/asvs/v4-ASVS-checklist-en.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidferreira/Universidade/Isep/1Ano/2Semestre/Desofs/Project/desofs2025_wed_ffs_4/Deliverables/Phase2/Sprint1/asvs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BB5CD3F-8937-6247-B6D3-85F07D391E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E6AF17-62BA-A147-9734-03BAD051DAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" tabRatio="500" firstSheet="6" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" tabRatio="500" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASVS Results" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="814">
   <si>
     <t>Security Category</t>
   </si>
@@ -2494,6 +2494,39 @@
   </si>
   <si>
     <t>This requirement is fulfilled by enforcing sequential business logic steps — such as plan selection, subscription creation, cancellation, renewal, and plan changes — while ensuring that only the authenticated user can perform these actions and that each step validates the current subscription state.</t>
+  </si>
+  <si>
+    <t>Upload size limits are configured in application.properties to prevent large file uploads and mitigate DoS risks</t>
+  </si>
+  <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/dashboardmanagement/api/DashboardController.java</t>
+  </si>
+  <si>
+    <t>Parameter minimization - Controllers use minimal params with @Valid validation (DashboardController.getDashboardView max 6 params)</t>
+  </si>
+  <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/usermanagement/services/UserService.java</t>
+  </si>
+  <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/usermanagement/services/LoginAttemptService.java</t>
+  </si>
+  <si>
+    <t>AuthApi.java implement sanitized audit logging without exposing sensitive data.</t>
+  </si>
+  <si>
+    <t>BCrypt password hashing, HTTPS enforcement, and JWT security provide approved encryption algorithms</t>
+  </si>
+  <si>
+    <t>UserService.deletePersonalData() implements comprehensive automated deletion with transactional safety and user anonymization</t>
+  </si>
+  <si>
+    <t>UserService.java systematically identifies sensitive data through exportPersonalData() method and enforces data classification via PersonalDataExportDTO structure</t>
+  </si>
+  <si>
+    <t>AuthApi accomplishes the sensitive data access auditing requirement through comprehensive logging of all authentication attempts, successful logins, and security events with proper data sanitization</t>
+  </si>
+  <si>
+    <t>The LoginAttemptService.loginFailed() in LoginAttemptService.java implements request monitoring by tracking attempt counts per user/IP, detecting threshold breaches (5 user, 20 IP), and triggering automatic blocks with security logging.</t>
   </si>
 </sst>
 </file>
@@ -2630,9 +2663,9 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF0E0E0E"/>
-      <name val=".AppleSystemUIFont"/>
+      <sz val="13"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -3955,7 +3988,7 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>55.555555555555557</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>100</c:v>
@@ -3967,7 +4000,7 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>16.666666666666664</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>71.428571428571431</c:v>
@@ -3976,7 +4009,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>49.132947976878611</c:v>
+                  <c:v>52.046783625730995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4707,15 +4740,15 @@
       </c>
       <c r="B9" s="10">
         <f>COUNTIF('Data Protection'!G2:G18,"Valid")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C9" s="11">
         <f>COUNTIF('Data Protection'!G2:G18,"&lt;&gt;Not Applicable")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="12">
         <f t="shared" si="0"/>
-        <v>55.555555555555557</v>
+        <v>100</v>
       </c>
       <c r="E9" s="13"/>
     </row>
@@ -4779,15 +4812,15 @@
       </c>
       <c r="B13" s="10">
         <f>COUNTIF('Files and Resources'!G2:G16,"Valid")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="11">
         <f>COUNTIF('Files and Resources'!G2:G16,"&lt;&gt;Not Applicable")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D13" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16.666666666666664</v>
       </c>
       <c r="E13" s="13"/>
     </row>
@@ -4833,15 +4866,15 @@
       </c>
       <c r="B16" s="10">
         <f>SUM(B2:B15)</f>
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C16" s="11">
         <f>SUM(C2:C15)</f>
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D16" s="12">
         <f t="shared" si="0"/>
-        <v>49.132947976878611</v>
+        <v>52.046783625730995</v>
       </c>
       <c r="E16" s="13"/>
     </row>
@@ -5521,7 +5554,7 @@
       <c r="H2" s="131" t="s">
         <v>89</v>
       </c>
-      <c r="I2" s="146" t="s">
+      <c r="I2" s="132" t="s">
         <v>802</v>
       </c>
       <c r="J2" s="66"/>
@@ -5743,7 +5776,7 @@
     <col min="11" max="1024" width="8.6640625" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="44" customFormat="1" ht="44">
+    <row r="1" spans="1:10" s="44" customFormat="1" ht="45" thickBot="1">
       <c r="A1" s="95" t="s">
         <v>20</v>
       </c>
@@ -5775,7 +5808,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="32.25" customHeight="1">
+    <row r="2" spans="1:10" ht="32.25" customHeight="1" thickBot="1">
       <c r="A2" s="141" t="s">
         <v>672</v>
       </c>
@@ -5793,13 +5826,17 @@
         <v>674</v>
       </c>
       <c r="G2" s="50" t="s">
-        <v>112</v>
-      </c>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
+        <v>26</v>
+      </c>
+      <c r="H2" s="50" t="s">
+        <v>600</v>
+      </c>
+      <c r="I2" s="132" t="s">
+        <v>803</v>
+      </c>
       <c r="J2" s="66"/>
     </row>
-    <row r="3" spans="1:10" ht="51">
+    <row r="3" spans="1:10" ht="52" thickBot="1">
       <c r="A3" s="141"/>
       <c r="B3" s="63" t="s">
         <v>675</v>
@@ -5815,7 +5852,7 @@
         <v>676</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="H3" s="29"/>
       <c r="I3" s="29"/>
@@ -12354,7 +12391,7 @@
       <c r="I2" s="50"/>
       <c r="J2" s="66"/>
     </row>
-    <row r="3" spans="1:10" ht="34">
+    <row r="3" spans="1:10" ht="35" thickBot="1">
       <c r="A3" s="141"/>
       <c r="B3" s="63" t="s">
         <v>562</v>
@@ -12376,7 +12413,7 @@
       <c r="I3" s="29"/>
       <c r="J3" s="33"/>
     </row>
-    <row r="4" spans="1:10" ht="34">
+    <row r="4" spans="1:10" ht="35" thickBot="1">
       <c r="A4" s="141"/>
       <c r="B4" s="63" t="s">
         <v>564</v>
@@ -12394,11 +12431,15 @@
       <c r="G4" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
+      <c r="H4" s="29" t="s">
+        <v>804</v>
+      </c>
+      <c r="I4" s="144" t="s">
+        <v>805</v>
+      </c>
       <c r="J4" s="33"/>
     </row>
-    <row r="5" spans="1:10" ht="34">
+    <row r="5" spans="1:10" ht="35" thickBot="1">
       <c r="A5" s="141"/>
       <c r="B5" s="63" t="s">
         <v>566</v>
@@ -12414,13 +12455,17 @@
         <v>567</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+        <v>26</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>806</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>813</v>
+      </c>
       <c r="J5" s="33"/>
     </row>
-    <row r="6" spans="1:10" ht="17">
+    <row r="6" spans="1:10" ht="18" thickBot="1">
       <c r="A6" s="141"/>
       <c r="B6" s="63" t="s">
         <v>568</v>
@@ -12481,7 +12526,9 @@
       <c r="F8" s="81" t="s">
         <v>574</v>
       </c>
-      <c r="G8" s="29"/>
+      <c r="G8" s="29" t="s">
+        <v>75</v>
+      </c>
       <c r="H8" s="29"/>
       <c r="I8" s="29"/>
       <c r="J8" s="33"/>
@@ -12580,7 +12627,7 @@
       </c>
       <c r="J12" s="33"/>
     </row>
-    <row r="13" spans="1:10" ht="34">
+    <row r="13" spans="1:10" ht="35" thickBot="1">
       <c r="A13" s="141"/>
       <c r="B13" s="63" t="s">
         <v>585</v>
@@ -12602,7 +12649,7 @@
       <c r="I13" s="29"/>
       <c r="J13" s="33"/>
     </row>
-    <row r="14" spans="1:10" ht="51">
+    <row r="14" spans="1:10" ht="52" thickBot="1">
       <c r="A14" s="141"/>
       <c r="B14" s="63" t="s">
         <v>587</v>
@@ -12620,11 +12667,15 @@
       <c r="G14" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
+      <c r="H14" s="29" t="s">
+        <v>806</v>
+      </c>
+      <c r="I14" s="144" t="s">
+        <v>811</v>
+      </c>
       <c r="J14" s="33"/>
     </row>
-    <row r="15" spans="1:10" ht="34">
+    <row r="15" spans="1:10" ht="35" thickBot="1">
       <c r="A15" s="141"/>
       <c r="B15" s="63" t="s">
         <v>589</v>
@@ -12642,11 +12693,15 @@
       <c r="G15" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
+      <c r="H15" s="29" t="s">
+        <v>806</v>
+      </c>
+      <c r="I15" s="144" t="s">
+        <v>808</v>
+      </c>
       <c r="J15" s="33"/>
     </row>
-    <row r="16" spans="1:10" ht="34">
+    <row r="16" spans="1:10" ht="35" thickBot="1">
       <c r="A16" s="141"/>
       <c r="B16" s="63" t="s">
         <v>591</v>
@@ -12662,13 +12717,17 @@
         <v>592</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
+        <v>26</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>524</v>
+      </c>
+      <c r="I16" s="144" t="s">
+        <v>812</v>
+      </c>
       <c r="J16" s="33"/>
     </row>
-    <row r="17" spans="1:10" ht="51">
+    <row r="17" spans="1:10" ht="52" thickBot="1">
       <c r="A17" s="141"/>
       <c r="B17" s="63" t="s">
         <v>593</v>
@@ -12686,11 +12745,15 @@
       <c r="G17" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
+      <c r="H17" s="29" t="s">
+        <v>807</v>
+      </c>
+      <c r="I17" s="146" t="s">
+        <v>809</v>
+      </c>
       <c r="J17" s="33"/>
     </row>
-    <row r="18" spans="1:10" ht="34">
+    <row r="18" spans="1:10" ht="35" thickBot="1">
       <c r="A18" s="141"/>
       <c r="B18" s="63" t="s">
         <v>595</v>
@@ -12706,10 +12769,14 @@
         <v>596</v>
       </c>
       <c r="G18" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
+        <v>26</v>
+      </c>
+      <c r="H18" s="36" t="s">
+        <v>806</v>
+      </c>
+      <c r="I18" s="144" t="s">
+        <v>810</v>
+      </c>
       <c r="J18" s="38"/>
     </row>
   </sheetData>
